--- a/output/Data and Chart Outputs/jamaica_gas.xlsx
+++ b/output/Data and Chart Outputs/jamaica_gas.xlsx
@@ -210,6 +210,18 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>

--- a/output/Data and Chart Outputs/jamaica_gas.xlsx
+++ b/output/Data and Chart Outputs/jamaica_gas.xlsx
@@ -155,6 +155,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Jamaica gas use (annual) (to 2025)</a:t>
             </a:r>
           </a:p>
